--- a/output/pdf_financials_xlsx/SXL.xlsx
+++ b/output/pdf_financials_xlsx/SXL.xlsx
@@ -6200,55 +6200,55 @@
         <v>1.938565</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.938565</v>
+        <v>0.415957</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3.12517</v>
+        <v>1.668618</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.715236</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.195612</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.15937</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.200986</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.11901</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.250159</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.54065</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.290491</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.164651</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.146337</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.381032</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.388282</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.147946</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.124348</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>0.119603</v>
       </c>
     </row>
     <row r="93">
@@ -7737,19 +7737,19 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0.160975</v>
+        <v>-1.602855</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.34293</v>
+        <v>-4.233872</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>6.849516</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>3.07708</v>
+        <v>2.840826</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.056825</v>
+        <v>-0.110539</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>0.002676</v>
@@ -10832,7 +10832,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -13038,7 +13042,11 @@
           <t>Warrants reserve (Notes 10)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -14158,7 +14166,11 @@
           <t>Warrants reserve (Notes 11)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -15524,7 +15536,11 @@
           <t>Warrants reserve (Notes 10 and 13)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -16554,7 +16570,11 @@
           <t>Warrants reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -17476,7 +17496,11 @@
           <t>Warrants reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -19426,7 +19450,11 @@
           <t>Warrants reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -22422,7 +22450,11 @@
           <t>Warrants reserve 8</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -37972,7 +38004,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E284" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SXL.xlsx
+++ b/output/pdf_financials_xlsx/SXL.xlsx
@@ -1101,10 +1101,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.057743</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0007560000000000001</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.008902</v>
@@ -2120,10 +2120,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.669405</v>
+        <v>-6.727148</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.547589</v>
+        <v>-0.548345</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.7221689999999999</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.669405</v>
+        <v>-6.727148</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.547589</v>
+        <v>-0.548345</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.7221689999999999</v>
@@ -2613,10 +2613,10 @@
         <v>0.07868</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.121557</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.310791</v>
       </c>
     </row>
     <row r="35">
@@ -2735,10 +2735,10 @@
         <v>0.12363</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.07373200000000001</v>
+        <v>0.195289</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0.204067</v>
+        <v>0.514858</v>
       </c>
     </row>
     <row r="37">
@@ -3467,10 +3467,10 @@
         <v>0.024535</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.128497</v>
+        <v>0.00694</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.319541</v>
+        <v>0.008750000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -8145,10 +8145,10 @@
         <v>0</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013523</v>
       </c>
       <c r="S124" s="3" t="n">
-        <v>0</v>
+        <v>-0.014296</v>
       </c>
     </row>
     <row r="125">
@@ -8206,10 +8206,10 @@
         <v>0</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013523</v>
       </c>
       <c r="S125" s="3" t="n">
-        <v>0</v>
+        <v>-0.014296</v>
       </c>
     </row>
     <row r="126">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -28536,7 +28536,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -55494,7 +55498,7 @@
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
@@ -57182,7 +57186,7 @@
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -59298,7 +59302,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -60562,7 +60566,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E502" s="5" t="n">

--- a/output/pdf_financials_xlsx/SXL.xlsx
+++ b/output/pdf_financials_xlsx/SXL.xlsx
@@ -1409,19 +1409,19 @@
         <v>1.746796</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.19459</v>
+        <v>0.129912</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.248024</v>
+        <v>0.255551</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0.949049</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.440015</v>
+        <v>-1.440015</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.132975</v>
+        <v>-0.132975</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1448,7 +1448,7 @@
         <v>-0</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.017703</v>
+        <v>-0.017703</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>-0</v>
@@ -2403,10 +2403,10 @@
         <v>-26.191181972005</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-35.53577591953088</v>
+        <v>-23.72436261502697</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-34.77295318583364</v>
+        <v>-35.82823823336843</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-103.3065084094123</v>
@@ -7279,22 +7279,22 @@
         <v>0</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.00192</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.007322</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.006992</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.000947</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>0.001119</v>
       </c>
       <c r="S110" s="3" t="n">
-        <v>0</v>
+        <v>0.002511</v>
       </c>
     </row>
     <row r="111">
@@ -7355,7 +7355,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019758</v>
       </c>
     </row>
     <row r="112">
@@ -7517,13 +7517,13 @@
         <v>0</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>0</v>
+        <v>-0.00701</v>
       </c>
       <c r="M114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0</v>
+        <v>-0.0038</v>
       </c>
       <c r="O114" s="3" t="n">
         <v>0</v>
@@ -7569,37 +7569,37 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.0926</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.082415</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.039503</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.06184</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.311369</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.269437</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.050848</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.036818</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>0.036882</v>
       </c>
       <c r="S115" s="3" t="n">
-        <v>0</v>
+        <v>0.248778</v>
       </c>
     </row>
     <row r="116">
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
       <c r="S134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019758</v>
       </c>
     </row>
     <row r="135">
@@ -8919,7 +8919,7 @@
         <v>-0.202844</v>
       </c>
       <c r="S135" s="3" t="n">
-        <v>-0.206344</v>
+        <v>-0.226102</v>
       </c>
     </row>
   </sheetData>
@@ -26306,7 +26306,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -28004,7 +28008,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -28216,7 +28224,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -29380,7 +29392,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr"/>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -31324,7 +31340,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -32320,7 +32340,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -32536,7 +32560,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -34348,7 +34376,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -36660,7 +36692,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -40580,7 +40616,11 @@
           <t>Future income tax (recovery)</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -41524,7 +41564,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E318" s="5" t="n">
         <v>-1.823538</v>
       </c>
@@ -48554,7 +48598,11 @@
           <t>Deferred income tax recovery (Note 15)</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -55082,7 +55130,11 @@
           <t>Deferred income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -59408,7 +59460,11 @@
           <t>Future income tax (recovery) (Note 9)</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E491" t="inlineStr">
         <is>
           <t>-</t>
